--- a/Beem Visa Debit - Dispute Management System Requirements.xlsx
+++ b/Beem Visa Debit - Dispute Management System Requirements.xlsx
@@ -594,7 +594,7 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>The Dispute Management System shall route a case to the Fraud team or the Payment Services team automatically, based on the agent's response to whether the member recognizes the transaction.</t>
+          <t>The Dispute Management System shall capture the agent's fraud/non-fraud classification of the dispute and queue the case to the corresponding team (Fraud or Payment Services) based on the recorded classification.</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
@@ -657,7 +657,7 @@
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>2. Dispute Triage</t>
+          <t>2. Dispute Triage (executed by the team assigned at intake: Fraud or Payment Services)</t>
         </is>
       </c>
       <c r="B13" s="5" t="n"/>
